--- a/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
+++ b/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
@@ -1465,7 +1465,7 @@
         <v>0.43</v>
       </c>
       <c r="E5">
-        <f>D5*每GW!$D$3</f>
+        <f>D5*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F5" s="3" t="n">
@@ -1500,7 +1500,7 @@
         <v>0.23</v>
       </c>
       <c r="E6">
-        <f>D6*每GW!$D$3</f>
+        <f>D6*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F6" s="3" t="n">
@@ -1535,7 +1535,7 @@
         <v>0.19</v>
       </c>
       <c r="E7">
-        <f>D7*每GW!$D$3</f>
+        <f>D7*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
@@ -1570,7 +1570,7 @@
         <v>0.04</v>
       </c>
       <c r="E8">
-        <f>D8*每GW!$D$3</f>
+        <f>D8*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
@@ -1605,7 +1605,7 @@
         <v>0.02</v>
       </c>
       <c r="E9">
-        <f>D9*每GW!$D$3</f>
+        <f>D9*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
@@ -1640,7 +1640,7 @@
         <v>0.003</v>
       </c>
       <c r="E10">
-        <f>D10*每GW!$D$3</f>
+        <f>D10*每GW!$D$2</f>
         <v/>
       </c>
       <c r="F10" s="3" t="n">

--- a/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
+++ b/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
@@ -3548,11 +3548,11 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1560</v>
+        <v>1605</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-22｜聚財網；鉅亨（10-23 收盤未取得）</t>
+          <t>2026-10-23｜台達電模型 In!E70（Yahoo 股市 10-24 頁面「昨收」）；10-22 收盤 1</t>
         </is>
       </c>
       <c r="H10">

--- a/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
+++ b/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
@@ -503,7 +503,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>公司模型：company-models 各公司 dist/*.xlsx（extract_models.py 抽數；AVGO 讀 PR #93 分支，未合併）。</t>
+          <t>公司模型：company-models 各公司 dist/*.xlsx（extract_models.py 抽數）。</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!B6</t>
+          <t>avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!B6</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 輸入與假設!C345</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 輸入與假設!C345</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 輸入與假設!C328</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 輸入與假設!C328</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 輸入與假設!C374</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 輸入與假設!C374</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!C33</t>
+          <t>avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!C33</t>
         </is>
       </c>
       <c r="J3" s="4" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!F35</t>
+          <t>avgo/dist/20261023_Broadcom模型_v0.1.xlsx Val!F35</t>
         </is>
       </c>
       <c r="N3">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>十年倍數待前瞻 P/E 歷史（Bloomberg）；規則值未算；模型在 PR #93，未合併</t>
+          <t>十年倍數待前瞻 P/E 歷史（Bloomberg）；規則值未算</t>
         </is>
       </c>
       <c r="Z3">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L15" s="4" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N15">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N16">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L17" s="4" t="n">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N17">

--- a/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
+++ b/markets/invest_map/dist/20261025_AI投資地圖_資料_v0.1.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -517,19 +517,26 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>可投資性口徑（預設，Andy 可改）：中心價＝各模型主口徑；半導體 P/E 類取「十年倍數規則值」與「Andy 先驗合理 P/E」兩者較低者；規則值不適用者（NVDA、AVGO、Ibiden）只用 Andy 合理 P/E，標「替代口徑」；記憶體以 P/B 規則值為主、P/E 規則值為對照；雲端與 neocloud 用模型加權目標價與情境下緣；MiniMax 用反向檢驗折現價值。空間＝隱含價 ÷ 10-23 收盤價 − 1，未折現。</t>
+          <t>收支關卡（Andy 2026-10-25 10:48）：先看收支、再看評價。模型期間（2026 起約五年）現金收支合計為負＝入不敷出、有資金缺口，不論估值空間多大，最終分級一律為「收支不足」。口徑：有自由現金流列者用自由現金流；雲端／neocloud 模板無此列者用「營運缺口（不含融資、不含還本）」；只有損益的半導體模型以「各情境淨利皆為正」判定（現金流本專案未建立）。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>分級：中心空間 ≥ 參數 tier_center 且下檔 ≥ tier_bear → 機會；中心 &lt; tier_rich → 偏貴；其餘 → 觀察。</t>
+          <t>可投資性口徑（預設，Andy 可改）：中心價＝各模型主口徑；半導體 P/E 類取「十年倍數規則值」與「Andy 先驗合理 P/E」兩者較低者；規則值不適用者（NVDA、AVGO、Ibiden）只用 Andy 合理 P/E，標「替代口徑」；記憶體以 P/B 規則值為主、P/E 規則值為對照；雲端與 neocloud 用模型加權目標價與情境下緣；MiniMax 用反向檢驗折現價值。空間＝隱含價 ÷ 10-23 收盤價 − 1，未折現。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>分級：中心空間 ≥ 參數 tier_center 且下檔 ≥ tier_bear → 機會；中心 &lt; tier_rich → 偏貴；其餘 → 觀察。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>本活頁簿是研究整理，不是投資建議；各模型的方法與假設見各自 README 與 Val／摘要頁。</t>
         </is>
@@ -3729,7 +3736,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 輸入與假設!C345</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 輸入與假設!C345</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -3766,7 +3773,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 輸入與假設!C328</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 輸入與假設!C328</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
@@ -3803,7 +3810,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 輸入與假設!C374</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 輸入與假設!C374</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
@@ -4041,7 +4048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4071,6 +4078,14 @@
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="10" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="30" customWidth="1" min="29" max="29"/>
+    <col width="46" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="44" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4209,6 +4224,46 @@
           <t>價格變動旗標</t>
         </is>
       </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>收支口徑</t>
+        </is>
+      </c>
+      <c r="AC1" s="2" t="inlineStr">
+        <is>
+          <t>收支列（模型）</t>
+        </is>
+      </c>
+      <c r="AD1" s="2" t="inlineStr">
+        <is>
+          <t>收支序列</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="inlineStr">
+        <is>
+          <t>期間合計</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>最小值</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>收支來源</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>收支關卡</t>
+        </is>
+      </c>
+      <c r="AI1" s="2" t="inlineStr">
+        <is>
+          <t>最終分級</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4301,6 +4356,40 @@
         <f>IF(Z2="","",IF(ABS(Z2)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>35 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE2" s="4" t="n">
+        <v>9831.987212663698</v>
+      </c>
+      <c r="AF2" s="4" t="n">
+        <v>112.494809527772</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>[Derived] nvidia/dist/20261023_NVIDIA模型_v0.1.1.xlsx PL!C12…PL!G292</t>
+        </is>
+      </c>
+      <c r="AH2">
+        <f>IF(AB2="淨利",IF(AF2&gt;0,"通過（淨利）","不通過"),IF(AE2&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI2">
+        <f>IF(AH2="不通過","收支不足",S2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4385,6 +4474,40 @@
         <f>IF(Z3="","",IF(ABS(Z3)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="n">
+        <v>2210.188539951681</v>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>33.728</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>[Derived] ../../../tmp/claude-0/avgo/avgo/dist/20261023_Broadcom模型_v0.1.xlsx PL!C13…PL!G229</t>
+        </is>
+      </c>
+      <c r="AH3">
+        <f>IF(AB3="淨利",IF(AF3&gt;0,"通過（淨利）","不通過"),IF(AE3&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI3">
+        <f>IF(AH3="不通過","收支不足",S3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4481,6 +4604,40 @@
         <f>IF(Z4="","",IF(ABS(Z4)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>自由現金流（淨利＋折舊 − 資本支出）</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026（基準） 232.9、2027 A 301.3、2028 A 334.4、2029 A 360.3、2027 B 293.3、2028 B 151.6、2029 B 327.4、2027 C 293.3、2028 C 77.1、2029 C 210.7</t>
+        </is>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>2582.300494403294</v>
+      </c>
+      <c r="AF4" s="4" t="n">
+        <v>77.12752837628589</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>[Derived] skhynix/dist/20261023_SK海力士模型_v0.4.1.xlsx Y!C22…Y!L22</t>
+        </is>
+      </c>
+      <c r="AH4">
+        <f>IF(AB4="淨利",IF(AF4&gt;0,"通過（淨利）","不通過"),IF(AE4&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI4">
+        <f>IF(AH4="不通過","收支不足",S4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4577,6 +4734,40 @@
         <f>IF(Z5="","",IF(ABS(Z5)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>自由現金流（淨利＋折舊 − 資本支出）</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026（基準） 291.2、2027 A 506.0、2028 A 561.3、2029 A 588.0、2027 B 492.5、2028 B 274.2、2029 B 555.8、2027 C 492.5、2028 C 165.3、2029 C 384.4</t>
+        </is>
+      </c>
+      <c r="AE5" s="4" t="n">
+        <v>4311.223913548546</v>
+      </c>
+      <c r="AF5" s="4" t="n">
+        <v>165.264961736399</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>[Derived] samsung/dist/20261023_三星電子模型_v0.2.1.xlsx Y!C22…Y!L22</t>
+        </is>
+      </c>
+      <c r="AH5">
+        <f>IF(AB5="淨利",IF(AF5&gt;0,"通過（淨利）","不通過"),IF(AE5&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI5">
+        <f>IF(AH5="不通過","收支不足",S5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4673,6 +4864,40 @@
         <f>IF(Z6="","",IF(ABS(Z6)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>自由現金流（淨利＋折舊 − 資本支出）</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>FY2026（基準） 67.1、FY2027 A 152.2、FY2028 A 172.3、FY2029 A 179.4、FY2027 B 154.2、FY2028 B 87.7、FY2029 B 132.0、FY2027 C 154.2、FY2028 C 59.6、FY2029 C 54.1</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="n">
+        <v>1212.84680356464</v>
+      </c>
+      <c r="AF6" s="4" t="n">
+        <v>54.0750248819423</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>[Derived] micron/dist/20261023_美光模型_v0.3.1.xlsx Y!C22…Y!L22</t>
+        </is>
+      </c>
+      <c r="AH6">
+        <f>IF(AB6="淨利",IF(AF6&gt;0,"通過（淨利）","不通過"),IF(AE6&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI6">
+        <f>IF(AH6="不通過","收支不足",S6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4774,6 +4999,40 @@
       </c>
       <c r="AA7">
         <f>IF(Z7="","",IF(ABS(Z7)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>10 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="n">
+        <v>1080.720589729756</v>
+      </c>
+      <c r="AF7" s="4" t="n">
+        <v>84.633409367754</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>[Derived] tsmc/dist/20261023_台積電模型_v0.2.1.xlsx PL!B12…PL!K12</t>
+        </is>
+      </c>
+      <c r="AH7">
+        <f>IF(AB7="淨利",IF(AF7&gt;0,"通過（淨利）","不通過"),IF(AE7&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI7">
+        <f>IF(AH7="不通過","收支不足",S7)</f>
         <v/>
       </c>
     </row>
@@ -4872,6 +5131,40 @@
         <f>IF(Z8="","",IF(ABS(Z8)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>184.2094367559607</v>
+      </c>
+      <c r="AF8" s="4" t="n">
+        <v>3.806</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>[Derived] arista/dist/20261024_Arista模型_v0.1.xlsx PL!C12…PL!G147</t>
+        </is>
+      </c>
+      <c r="AH8">
+        <f>IF(AB8="淨利",IF(AF8&gt;0,"通過（淨利）","不通過"),IF(AE8&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI8">
+        <f>IF(AH8="不通過","收支不足",S8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4970,6 +5263,40 @@
       </c>
       <c r="AA9">
         <f>IF(Z9="","",IF(ABS(Z9)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="n">
+        <v>1214.705294278893</v>
+      </c>
+      <c r="AF9" s="4" t="n">
+        <v>10.797</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>[Derived] innolight/dist/20261024_中際旭創模型_v0.1.xlsx PL!C12…PL!G149</t>
+        </is>
+      </c>
+      <c r="AH9">
+        <f>IF(AB9="淨利",IF(AF9&gt;0,"通過（淨利）","不通過"),IF(AE9&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI9">
+        <f>IF(AH9="不通過","收支不足",S9)</f>
         <v/>
       </c>
     </row>
@@ -5068,6 +5395,40 @@
         <f>IF(Z10="","",IF(ABS(Z10)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE10" s="4" t="n">
+        <v>4047.392536240182</v>
+      </c>
+      <c r="AF10" s="4" t="n">
+        <v>60.108</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>[Derived] delta/dist/20261024_台達電模型_v0.1.xlsx PL!C13…PL!G171</t>
+        </is>
+      </c>
+      <c r="AH10">
+        <f>IF(AB10="淨利",IF(AF10&gt;0,"通過（淨利）","不通過"),IF(AE10&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI10">
+        <f>IF(AH10="不通過","收支不足",S10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5164,6 +5525,40 @@
         <f>IF(Z11="","",IF(ABS(Z11)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="n">
+        <v>4153.221447696762</v>
+      </c>
+      <c r="AF11" s="4" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>[Derived] quanta/dist/20261024_廣達模型_v0.1.xlsx PL!C13…PL!G171</t>
+        </is>
+      </c>
+      <c r="AH11">
+        <f>IF(AB11="淨利",IF(AF11&gt;0,"通過（淨利）","不通過"),IF(AE11&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI11">
+        <f>IF(AH11="不通過","收支不足",S11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5246,6 +5641,40 @@
       </c>
       <c r="AA12">
         <f>IF(Z12="","",IF(ABS(Z12)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="n">
+        <v>2912.837454335999</v>
+      </c>
+      <c r="AF12" s="4" t="n">
+        <v>63.713</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>[Derived] ibiden/dist/20261024_Ibiden模型_v0.1.xlsx PL!C11…PL!G156</t>
+        </is>
+      </c>
+      <c r="AH12">
+        <f>IF(AB12="淨利",IF(AF12&gt;0,"通過（淨利）","不通過"),IF(AE12&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI12">
+        <f>IF(AH12="不通過","收支不足",S12)</f>
         <v/>
       </c>
     </row>
@@ -5323,6 +5752,40 @@
         <f>IF(Z13="","",IF(ABS(Z13)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="n">
+        <v>20374.08496527686</v>
+      </c>
+      <c r="AF13" s="4" t="n">
+        <v>375.4</v>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>[Derived] advantest/dist/20261023_Advantest模型_v0.2.2.xlsx PL!C12…PL!G122</t>
+        </is>
+      </c>
+      <c r="AH13">
+        <f>IF(AB13="淨利",IF(AF13&gt;0,"通過（淨利）","不通過"),IF(AE13&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI13">
+        <f>IF(AH13="不通過","收支不足",S13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5398,6 +5861,40 @@
         <f>IF(Z14="","",IF(ABS(Z14)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>淨利</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>PL 頁各情境淨利</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>30 個情境年度淨利，全部 為正</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="n">
+        <v>5014.645076769742</v>
+      </c>
+      <c r="AF14" s="4" t="n">
+        <v>135.521</v>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>[Derived] disco/dist/20261023_Disco模型_v0.1.3.xlsx PL!C16…PL!G244</t>
+        </is>
+      </c>
+      <c r="AH14">
+        <f>IF(AB14="淨利",IF(AF14&gt;0,"通過（淨利）","不通過"),IF(AE14&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI14">
+        <f>IF(AH14="不通過","收支不足",S14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5429,7 +5926,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
@@ -5437,7 +5934,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L15" s="4" t="n">
@@ -5445,7 +5942,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>microsoft/dist/20261022_Microsoft收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N15">
@@ -5485,6 +5982,40 @@
         <f>IF(Z15="","",IF(ABS(Z15)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>FY27 1.2、FY28 37.2、FY29 80.5、FY30 88.3、FY31 23.3</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="n">
+        <v>230.4767517004849</v>
+      </c>
+      <c r="AF15" s="4" t="n">
+        <v>1.24629259914113</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>[Derived] microsoft/dist/20261025_Microsoft收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+        </is>
+      </c>
+      <c r="AH15">
+        <f>IF(AB15="淨利",IF(AF15&gt;0,"通過（淨利）","不通過"),IF(AE15&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI15">
+        <f>IF(AH15="不通過","收支不足",S15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5516,7 +6047,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
@@ -5524,7 +6055,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L16" s="4" t="n">
@@ -5532,7 +6063,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>amazon/dist/20261022_Amazon收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N16">
@@ -5572,6 +6103,40 @@
         <f>IF(Z16="","",IF(ABS(Z16)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026 -60.0、2027 -67.6、2028 -29.8、2029 10.0、2030 -66.4</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="n">
+        <v>-213.784581805032</v>
+      </c>
+      <c r="AF16" s="4" t="n">
+        <v>-67.6423913811975</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>[Derived] amazon/dist/20261025_Amazon收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+        </is>
+      </c>
+      <c r="AH16">
+        <f>IF(AB16="淨利",IF(AF16&gt;0,"通過（淨利）","不通過"),IF(AE16&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI16">
+        <f>IF(AH16="不通過","收支不足",S16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5603,7 +6168,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
@@ -5611,7 +6176,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C7</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C7</t>
         </is>
       </c>
       <c r="L17" s="4" t="n">
@@ -5619,7 +6184,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>alphabet/dist/20261022_Alphabet收支模型_v0_2_1.xlsx 摘要!C10</t>
+          <t>alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 摘要!C10</t>
         </is>
       </c>
       <c r="N17">
@@ -5659,6 +6224,40 @@
         <f>IF(Z17="","",IF(ABS(Z17)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>自由現金流（FCF＝營運現金 − 現金資本支出）</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026 -4.1、2027 -6.4、2028 16.0、2029 28.3、2030 -62.3</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="n">
+        <v>-28.49105701735244</v>
+      </c>
+      <c r="AF17" s="4" t="n">
+        <v>-62.3373425541111</v>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>[Derived] alphabet/dist/20261025_Alphabet收支模型_v0_2_2.xlsx 各期收支!C44…各期收支!G44</t>
+        </is>
+      </c>
+      <c r="AH17">
+        <f>IF(AB17="淨利",IF(AF17&gt;0,"通過（淨利）","不通過"),IF(AE17&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI17">
+        <f>IF(AH17="不通過","收支不足",S17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5746,6 +6345,40 @@
         <f>IF(Z18="","",IF(ABS(Z18)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>營運缺口（不含融資、不含還本）</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY27 -32.1、FY28 -27.5、FY29 17.4、FY30 3.6、FY31 2.0</t>
+        </is>
+      </c>
+      <c r="AE18" s="4" t="n">
+        <v>-36.65954451431514</v>
+      </c>
+      <c r="AF18" s="4" t="n">
+        <v>-32.1477872210438</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>[Derived] oracle/dist/20261022_Oracle收支模型_v0_3_1.xlsx 各期收支!C50…各期收支!G50</t>
+        </is>
+      </c>
+      <c r="AH18">
+        <f>IF(AB18="淨利",IF(AF18&gt;0,"通過（淨利）","不通過"),IF(AE18&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI18">
+        <f>IF(AH18="不通過","收支不足",S18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5833,6 +6466,40 @@
         <f>IF(Z19="","",IF(ABS(Z19)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>營運缺口（不含融資、不含還本）</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>FY26 -28.0、FY27 -30.4、FY28 -17.6、FY29 -13.4、FY30 -16.3</t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="n">
+        <v>-105.7055627525181</v>
+      </c>
+      <c r="AF19" s="4" t="n">
+        <v>-30.399857894978</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>[Derived] coreweave/dist/20261021_CoreWeave收支模型_v4_12.xlsx 各期收支!C39…各期收支!G39</t>
+        </is>
+      </c>
+      <c r="AH19">
+        <f>IF(AB19="淨利",IF(AF19&gt;0,"通過（淨利）","不通過"),IF(AE19&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI19">
+        <f>IF(AH19="不通過","收支不足",S19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5920,6 +6587,40 @@
         <f>IF(Z20="","",IF(ABS(Z20)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>營運缺口（不含融資、不含還本）</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>FY26 -15.1、FY27 -17.9、FY28 -18.2、FY29 -17.2、FY30 -25.5</t>
+        </is>
+      </c>
+      <c r="AE20" s="4" t="n">
+        <v>-94.001644749039</v>
+      </c>
+      <c r="AF20" s="4" t="n">
+        <v>-25.5402170366338</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>[Derived] nebius/dist/20261022_Nebius收支模型_v0_5.xlsx 各期收支!C45…各期收支!G45</t>
+        </is>
+      </c>
+      <c r="AH20">
+        <f>IF(AB20="淨利",IF(AF20&gt;0,"通過（淨利）","不通過"),IF(AE20&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI20">
+        <f>IF(AH20="不通過","收支不足",S20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6005,6 +6706,40 @@
       </c>
       <c r="AA21">
         <f>IF(Z21="","",IF(ABS(Z21)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>營運缺口（不含融資、不含還本）</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>FY26 -371.1、FY27 -383.6、FY28 -40.7、FY29 -1.9、FY30 -22.2</t>
+        </is>
+      </c>
+      <c r="AE21" s="4" t="n">
+        <v>-819.4510890267885</v>
+      </c>
+      <c r="AF21" s="4" t="n">
+        <v>-383.618038613095</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>[Derived] whitefiber/dist/20261022_WhiteFiber收支模型_v0_2.xlsx 各期收支!C52…各期收支!G52</t>
+        </is>
+      </c>
+      <c r="AH21">
+        <f>IF(AB21="淨利",IF(AF21&gt;0,"通過（淨利）","不通過"),IF(AE21&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI21">
+        <f>IF(AH21="不通過","收支不足",S21)</f>
         <v/>
       </c>
     </row>
@@ -6087,6 +6822,40 @@
         <f>IF(Z22="","",IF(ABS(Z22)&gt;0.2,"模型尚未反映期間變化",""))</f>
         <v/>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>F06</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>FY2026 -578.3、FY2027 -826.5、FY2028 -1,129.9、FY2029 -1,433.3、FY2030 -1,693.3</t>
+        </is>
+      </c>
+      <c r="AE22" s="4" t="n">
+        <v>-5661.185548552452</v>
+      </c>
+      <c r="AF22" s="4" t="n">
+        <v>-1693.27864140096</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>[Derived] minimax/dist/20261022_MiniMax收支模型_v0_2.xlsx Funding!E13…Funding!I13</t>
+        </is>
+      </c>
+      <c r="AH22">
+        <f>IF(AB22="淨利",IF(AF22&gt;0,"通過（淨利）","不通過"),IF(AE22&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI22">
+        <f>IF(AH22="不通過","收支不足",S22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6133,6 +6902,40 @@
       </c>
       <c r="AA23">
         <f>IF(Z23="","",IF(ABS(Z23)&gt;0.2,"模型尚未反映期間變化",""))</f>
+        <v/>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>現金流</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>F09</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2026 -41.3、2027 -40.9、2028 -40.5、2029 -59.4、2030 -99.1</t>
+        </is>
+      </c>
+      <c r="AE23" s="4" t="n">
+        <v>-281.188184190984</v>
+      </c>
+      <c r="AF23" s="4" t="n">
+        <v>-99.0538108419448</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>[Derived] zhipu/dist/20261022_智譜收支模型_v0_1_1.xlsx Funding!E16…Funding!I16</t>
+        </is>
+      </c>
+      <c r="AH23">
+        <f>IF(AB23="淨利",IF(AF23&gt;0,"通過（淨利）","不通過"),IF(AE23&lt;0,"不通過","通過（現金流）"))</f>
+        <v/>
+      </c>
+      <c r="AI23">
+        <f>IF(AH23="不通過","收支不足",S23)</f>
         <v/>
       </c>
     </row>
